--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_12-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_12-09-2025.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>£10.95</t>
+          <t>£10.90</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>£15.99</t>
+          <t>£15.70</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>£16.60</t>
+          <t>£15.99</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>£20.59</t>
+          <t>£20.25</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>£22.76</t>
+          <t>£22.23</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>£28.80</t>
+          <t>£27.90</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>£27.95</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>£34.95</t>
+          <t>£34.80</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>£42.00</t>
+          <t>£41.90</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://insulation4less.co.uk/products/150mm-celotex-xr4150-2-4m-x-1-2m</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>£43.50</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>£43.50</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>£43.50</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>£43.50</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>£43.50</t>
+          <t>£41.80</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
